--- a/Sprint_Report/TeamEReport.xlsx
+++ b/Sprint_Report/TeamEReport.xlsx
@@ -17,14 +17,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId13" roundtripDataChecksum="1FhkoI79Ex+y+ilrFaRfHV+0M1kKX50C00rnat2aRKw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId13" roundtripDataChecksum="YLl0kjukACnVyuA44K/BsI9gUn+5ZJuj3vmUErRJ+UY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="207">
   <si>
     <t>Initials</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t xml:space="preserve">Correct gender for role </t>
+  </si>
+  <si>
+    <t>coding</t>
   </si>
   <si>
     <t>US08</t>
@@ -351,6 +354,18 @@
   </si>
   <si>
     <t>Late Completion</t>
+  </si>
+  <si>
+    <t>Correct Gender for role</t>
+  </si>
+  <si>
+    <t>marriage before death</t>
+  </si>
+  <si>
+    <t>under 150 years old</t>
+  </si>
+  <si>
+    <t>Sibling Spacing (8 months apart)</t>
   </si>
   <si>
     <t>Story Description</t>
@@ -723,10 +738,10 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -734,6 +749,12 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -743,14 +764,8 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -799,11 +814,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="647259374"/>
-        <c:axId val="473908266"/>
+        <c:axId val="1113012086"/>
+        <c:axId val="993125955"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="647259374"/>
+        <c:axId val="1113012086"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -855,10 +870,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="473908266"/>
+        <c:crossAx val="993125955"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="473908266"/>
+        <c:axId val="993125955"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -922,7 +937,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="647259374"/>
+        <c:crossAx val="1113012086"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -963,11 +978,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="294652514"/>
-        <c:axId val="707119878"/>
+        <c:axId val="949758386"/>
+        <c:axId val="1096522443"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="294652514"/>
+        <c:axId val="949758386"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1019,10 +1034,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="707119878"/>
+        <c:crossAx val="1096522443"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="707119878"/>
+        <c:axId val="1096522443"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1086,7 +1101,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="294652514"/>
+        <c:crossAx val="949758386"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -3208,196 +3223,238 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="7">
+        <v>2.0</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>5</v>
       </c>
+      <c r="E8" s="7" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="7">
+        <v>2.0</v>
+      </c>
       <c r="B9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="8">
+      <c r="A10" s="7">
         <v>1.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>39</v>
+      <c r="E10" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="7">
+        <v>2.0</v>
+      </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>10</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
+      <c r="A14" s="7">
+        <v>2.0</v>
+      </c>
       <c r="B14" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
+      <c r="A16" s="7">
+        <v>2.0</v>
+      </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="B22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
+      <c r="A23" s="7">
+        <v>2.0</v>
+      </c>
       <c r="B23" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>10</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
       <c r="B24" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="B25" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="7" t="s">
+      <c r="B25" s="8" t="s">
         <v>77</v>
       </c>
+      <c r="C25" s="8" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="B26" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="C26" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4400,19 +4457,19 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F1" s="10"/>
     </row>
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F2" s="10"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F3" s="10"/>
     </row>
@@ -4422,13 +4479,13 @@
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F5" s="10"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -4438,7 +4495,7 @@
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -4467,22 +4524,22 @@
         <v>22</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -4506,7 +4563,7 @@
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13">
         <v>42527.0</v>
@@ -4522,7 +4579,7 @@
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" s="13">
         <v>42540.0</v>
@@ -4547,7 +4604,7 @@
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B17" s="13">
         <v>42554.0</v>
@@ -4572,7 +4629,7 @@
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B18" s="13">
         <v>42568.0</v>
@@ -4597,7 +4654,7 @@
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B19" s="13">
         <v>42582.0</v>
@@ -8570,22 +8627,22 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -8615,13 +8672,13 @@
       <c r="B2" s="2">
         <v>24.0</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="8">
         <v>0.0</v>
       </c>
       <c r="D2" s="2">
         <v>0.0</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <v>0.0</v>
       </c>
       <c r="F2" s="10">
@@ -8638,18 +8695,27 @@
       <c r="C3" s="2">
         <v>6.0</v>
       </c>
-      <c r="D3" s="2">
-        <v>616.0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>500.0</v>
+      <c r="D3" s="16">
+        <v>672.0</v>
+      </c>
+      <c r="E3" s="16">
+        <v>580.0</v>
       </c>
       <c r="F3" s="10">
         <v>73.9</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="9"/>
+      <c r="A4" s="17">
+        <v>46201.0</v>
+      </c>
+      <c r="B4" s="7">
+        <v>12.0</v>
+      </c>
+      <c r="C4" s="7">
+        <v>6.0</v>
+      </c>
+      <c r="D4" s="7"/>
       <c r="F4" s="10"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
@@ -12665,7 +12731,7 @@
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -12674,20 +12740,20 @@
       <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="E1" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="F1" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="G1" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="H1" s="19" t="s">
         <v>101</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
@@ -12720,28 +12786,28 @@
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="8">
         <v>141.0</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="8">
         <v>120.0</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="8">
         <v>141.0</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="8">
         <v>120.0</v>
       </c>
       <c r="I3" s="9">
@@ -12753,7 +12819,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -12761,16 +12827,16 @@
       <c r="D4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <v>110.0</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="8">
         <v>60.0</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="8">
         <v>110.0</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="8">
         <v>60.0</v>
       </c>
       <c r="I4" s="9">
@@ -12791,12 +12857,20 @@
         <v>29</v>
       </c>
       <c r="E5" s="7">
-        <v>110.0</v>
-      </c>
-      <c r="F5" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="F5" s="8">
         <v>60.0</v>
       </c>
-      <c r="I5" s="9"/>
+      <c r="G5" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>30.0</v>
+      </c>
+      <c r="I5" s="17">
+        <v>46190.0</v>
+      </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="2" t="s">
@@ -12811,16 +12885,16 @@
       <c r="D6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <v>100.0</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <v>45.0</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <v>92.0</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <v>50.0</v>
       </c>
       <c r="I6" s="9">
@@ -12828,28 +12902,28 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <v>250.0</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <v>45.0</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <v>273.0</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="8">
         <v>60.0</v>
       </c>
       <c r="I7" s="9">
@@ -12857,31 +12931,31 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="19" t="s">
+      <c r="A8" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="16">
         <v>50.0</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="16">
         <v>75.0</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>21.0</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>80.0</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="17">
         <v>46191.0</v>
       </c>
     </row>
@@ -12913,8 +12987,8 @@
       <c r="I13" s="9"/>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="B14" s="16" t="s">
-        <v>104</v>
+      <c r="B14" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="I14" s="9"/>
     </row>
@@ -12923,14 +12997,14 @@
       <c r="I15" s="9"/>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="B16" s="16" t="s">
-        <v>105</v>
+      <c r="B16" s="18" t="s">
+        <v>106</v>
       </c>
       <c r="I16" s="9"/>
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="B17" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I17" s="9"/>
     </row>
@@ -12943,14 +13017,14 @@
       <c r="I19" s="9"/>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="B20" s="16" t="s">
-        <v>107</v>
+      <c r="B20" s="18" t="s">
+        <v>108</v>
       </c>
       <c r="I20" s="9"/>
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I21" s="9"/>
     </row>
@@ -16892,7 +16966,7 @@
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -16901,28 +16975,142 @@
       <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="E1" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="F1" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="G1" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="H1" s="19" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="2" ht="12.75" customHeight="1"/>
-    <row r="3" ht="12.75" customHeight="1"/>
-    <row r="4" ht="12.75" customHeight="1"/>
-    <row r="5" ht="12.75" customHeight="1"/>
-    <row r="6" ht="12.75" customHeight="1"/>
-    <row r="7" ht="12.75" customHeight="1"/>
+      <c r="I1" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="F2" s="7">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="F3" s="7">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="4" ht="12.75" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="7">
+        <v>15.0</v>
+      </c>
+      <c r="F4" s="7">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="5" ht="12.75" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="7">
+        <v>15.0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="7" ht="12.75" customHeight="1">
+      <c r="A7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>45.0</v>
+      </c>
+    </row>
     <row r="8" ht="12.75" customHeight="1"/>
     <row r="9" ht="12.75" customHeight="1"/>
     <row r="10" ht="12.75" customHeight="1"/>
@@ -17938,7 +18126,7 @@
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -17947,20 +18135,20 @@
       <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="E1" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="F1" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="G1" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="H1" s="19" t="s">
         <v>101</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1"/>
@@ -18984,7 +19172,7 @@
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -18993,20 +19181,20 @@
       <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="E1" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="F1" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="G1" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="H1" s="19" t="s">
         <v>101</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1"/>
@@ -20036,8 +20224,8 @@
       <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="16" t="s">
-        <v>109</v>
+      <c r="C1" s="18" t="s">
+        <v>114</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -20068,10 +20256,10 @@
         <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
@@ -20079,10 +20267,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
@@ -20090,21 +20278,21 @@
         <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
@@ -20112,10 +20300,10 @@
         <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
@@ -20123,10 +20311,10 @@
         <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
@@ -20134,395 +20322,395 @@
         <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="C20" s="23" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">

--- a/Sprint_Report/TeamEReport.xlsx
+++ b/Sprint_Report/TeamEReport.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="211">
   <si>
     <t>Initials</t>
   </si>
@@ -368,6 +368,21 @@
     <t>Sibling Spacing (8 months apart)</t>
   </si>
   <si>
+    <t xml:space="preserve">Completing Stories on Time: All 6 planned user stories were implemented and verified against the test GEDCOM file by the sprint deadline. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good Communication: Team members met for weekly zoom meeting and communicated throughout the week through messaging to divide GEDCOM user stories and resolve issues. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relying on a single testfile: Team members will create a new testfile for each user story to cover normal cases, edge cases and boundary conditions. </t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Multiple Births &lt;= 5</t>
+  </si>
+  <si>
     <t>Story Description</t>
   </si>
   <si>
@@ -459,9 +474,6 @@
   </si>
   <si>
     <t>Siblings should not marry one another</t>
-  </si>
-  <si>
-    <t>First cousins should not marry one another</t>
   </si>
   <si>
     <t>Aunts and uncles</t>
@@ -651,9 +663,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="mm/dd"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -726,7 +739,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -769,6 +782,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -814,11 +830,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="1113012086"/>
-        <c:axId val="993125955"/>
+        <c:axId val="1411270868"/>
+        <c:axId val="301430367"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1113012086"/>
+        <c:axId val="1411270868"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -870,10 +886,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="993125955"/>
+        <c:crossAx val="301430367"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="993125955"/>
+        <c:axId val="301430367"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -937,7 +953,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1113012086"/>
+        <c:crossAx val="1411270868"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -978,11 +994,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="949758386"/>
-        <c:axId val="1096522443"/>
+        <c:axId val="1397272643"/>
+        <c:axId val="249227662"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="949758386"/>
+        <c:axId val="1397272643"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1034,10 +1050,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1096522443"/>
+        <c:crossAx val="249227662"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1096522443"/>
+        <c:axId val="249227662"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1101,7 +1117,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="949758386"/>
+        <c:crossAx val="1397272643"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -3287,10 +3303,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="7">
+        <v>3.0</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>51</v>
       </c>
@@ -3302,6 +3321,9 @@
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="7">
+        <v>3.0</v>
+      </c>
       <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
@@ -3326,10 +3348,13 @@
         <v>15</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
+      <c r="A15" s="7">
+        <v>3.0</v>
+      </c>
       <c r="B15" s="2" t="s">
         <v>57</v>
       </c>
@@ -3354,10 +3379,13 @@
         <v>15</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
+      <c r="A17" s="7">
+        <v>3.0</v>
+      </c>
       <c r="B17" s="2" t="s">
         <v>61</v>
       </c>
@@ -3425,7 +3453,7 @@
         <v>10</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
@@ -8702,7 +8730,8 @@
         <v>580.0</v>
       </c>
       <c r="F3" s="10">
-        <v>73.9</v>
+        <f t="shared" ref="F3:F6" si="1">(D3-D2)/E3*60</f>
+        <v>69.51724138</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
@@ -8715,16 +8744,46 @@
       <c r="C4" s="7">
         <v>6.0</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="F4" s="10"/>
+      <c r="D4" s="7">
+        <v>395.0</v>
+      </c>
+      <c r="E4" s="7">
+        <v>262.0</v>
+      </c>
+      <c r="F4" s="10">
+        <f t="shared" si="1"/>
+        <v>-63.4351145</v>
+      </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="9"/>
-      <c r="F5" s="10"/>
+      <c r="A5" s="17">
+        <v>46208.0</v>
+      </c>
+      <c r="B5" s="7">
+        <v>6.0</v>
+      </c>
+      <c r="C5" s="7">
+        <v>6.0</v>
+      </c>
+      <c r="F5" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="F6" s="10"/>
+      <c r="A6" s="17">
+        <v>46215.0</v>
+      </c>
+      <c r="B6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="7">
+        <v>6.0</v>
+      </c>
+      <c r="F6" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="9"/>
@@ -16959,7 +17018,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="10.78"/>
+    <col customWidth="1" min="1" max="1" width="10.78"/>
+    <col customWidth="1" min="2" max="2" width="28.56"/>
+    <col customWidth="1" min="3" max="26" width="10.78"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -17002,13 +17063,22 @@
         <v>5</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E2" s="7">
         <v>10.0</v>
       </c>
       <c r="F2" s="7">
         <v>60.0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>27.0</v>
+      </c>
+      <c r="H2" s="7">
+        <v>36.0</v>
+      </c>
+      <c r="I2" s="23">
+        <v>46199.0</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
@@ -17022,13 +17092,22 @@
         <v>5</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E3" s="7">
         <v>10.0</v>
       </c>
       <c r="F3" s="7">
         <v>60.0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>70.0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>75.0</v>
+      </c>
+      <c r="I3" s="23">
+        <v>46200.0</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
@@ -17042,13 +17121,22 @@
         <v>10</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E4" s="7">
         <v>15.0</v>
       </c>
       <c r="F4" s="7">
         <v>45.0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>22.0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>39.0</v>
+      </c>
+      <c r="I4" s="23">
+        <v>46199.0</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
@@ -17062,13 +17150,22 @@
         <v>10</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E5" s="7">
         <v>15.0</v>
       </c>
       <c r="F5" s="7">
         <v>45.0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>25.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>27.0</v>
+      </c>
+      <c r="I5" s="23">
+        <v>46199.0</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
@@ -17082,13 +17179,22 @@
         <v>15</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E6" s="7">
         <v>20.0</v>
       </c>
       <c r="F6" s="7">
         <v>45.0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>130.0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>40.0</v>
+      </c>
+      <c r="I6" s="23">
+        <v>46199.0</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
@@ -17102,13 +17208,22 @@
         <v>15</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E7" s="7">
         <v>20.0</v>
       </c>
       <c r="F7" s="7">
         <v>45.0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>121.0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>45.0</v>
+      </c>
+      <c r="I7" s="23">
+        <v>46199.0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1"/>
@@ -17117,15 +17232,45 @@
     <row r="11" ht="12.75" customHeight="1"/>
     <row r="12" ht="12.75" customHeight="1"/>
     <row r="13" ht="12.75" customHeight="1"/>
-    <row r="14" ht="12.75" customHeight="1"/>
-    <row r="15" ht="12.75" customHeight="1"/>
-    <row r="16" ht="12.75" customHeight="1"/>
-    <row r="17" ht="12.75" customHeight="1"/>
-    <row r="18" ht="12.75" customHeight="1"/>
-    <row r="19" ht="12.75" customHeight="1"/>
-    <row r="20" ht="12.75" customHeight="1"/>
-    <row r="21" ht="12.75" customHeight="1"/>
-    <row r="22" ht="12.75" customHeight="1"/>
+    <row r="14" ht="12.75" customHeight="1">
+      <c r="B14" s="18" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" ht="12.75" customHeight="1">
+      <c r="B15" s="22"/>
+    </row>
+    <row r="16" ht="12.75" customHeight="1">
+      <c r="B16" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" ht="62.25" customHeight="1">
+      <c r="B17" s="21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" ht="63.75" customHeight="1">
+      <c r="B18" s="21" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" ht="12.75" customHeight="1">
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" ht="12.75" customHeight="1">
+      <c r="B20" s="18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" ht="61.5" customHeight="1">
+      <c r="B21" s="21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" ht="12.75" customHeight="1">
+      <c r="B22" s="7"/>
+    </row>
     <row r="23" ht="12.75" customHeight="1"/>
     <row r="24" ht="12.75" customHeight="1"/>
     <row r="25" ht="12.75" customHeight="1"/>
@@ -18119,7 +18264,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="10.78"/>
+    <col customWidth="1" min="1" max="1" width="10.78"/>
+    <col customWidth="1" min="2" max="2" width="19.67"/>
+    <col customWidth="1" min="3" max="26" width="10.78"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -18151,10 +18298,86 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" ht="12.75" customHeight="1"/>
-    <row r="3" ht="12.75" customHeight="1"/>
-    <row r="4" ht="12.75" customHeight="1"/>
-    <row r="5" ht="12.75" customHeight="1"/>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="F2" s="7">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" s="7">
+        <v>15.0</v>
+      </c>
+      <c r="F3" s="7">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="4" ht="12.75" customHeight="1">
+      <c r="A4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="7">
+        <v>25.0</v>
+      </c>
+      <c r="F4" s="7">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="5" ht="12.75" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>45.0</v>
+      </c>
+    </row>
     <row r="6" ht="12.75" customHeight="1"/>
     <row r="7" ht="12.75" customHeight="1"/>
     <row r="8" ht="12.75" customHeight="1"/>
@@ -20225,7 +20448,7 @@
         <v>24</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -20258,8 +20481,8 @@
       <c r="B2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>115</v>
+      <c r="C2" s="24" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
@@ -20267,10 +20490,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>117</v>
+        <v>121</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
@@ -20280,19 +20503,19 @@
       <c r="B4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>118</v>
+      <c r="C4" s="24" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>121</v>
+        <v>125</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
@@ -20300,10 +20523,10 @@
         <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>123</v>
+        <v>127</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
@@ -20311,10 +20534,10 @@
         <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>125</v>
+        <v>129</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
@@ -20322,10 +20545,10 @@
         <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>127</v>
+        <v>131</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
@@ -20333,10 +20556,10 @@
         <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>129</v>
+        <v>133</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
@@ -20344,10 +20567,10 @@
         <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>131</v>
+        <v>135</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
@@ -20357,8 +20580,8 @@
       <c r="B11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>132</v>
+      <c r="C11" s="24" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
@@ -20368,8 +20591,8 @@
       <c r="B12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>133</v>
+      <c r="C12" s="24" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
@@ -20377,10 +20600,10 @@
         <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>135</v>
+        <v>139</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
@@ -20388,10 +20611,10 @@
         <v>55</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>137</v>
+        <v>141</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
@@ -20401,8 +20624,8 @@
       <c r="B15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="23" t="s">
-        <v>138</v>
+      <c r="C15" s="24" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
@@ -20410,10 +20633,10 @@
         <v>59</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>140</v>
+        <v>144</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
@@ -20421,10 +20644,10 @@
         <v>61</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>142</v>
+        <v>146</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
@@ -20434,8 +20657,8 @@
       <c r="B18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="23" t="s">
-        <v>143</v>
+      <c r="C18" s="24" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
@@ -20445,8 +20668,8 @@
       <c r="B19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="23" t="s">
-        <v>144</v>
+      <c r="C19" s="24" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
@@ -20456,18 +20679,16 @@
       <c r="B20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="23" t="s">
-        <v>145</v>
-      </c>
+      <c r="C20" s="24"/>
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C21" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="24" t="s">
         <v>64</v>
       </c>
     </row>
@@ -20476,10 +20697,10 @@
         <v>71</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>148</v>
+        <v>151</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
@@ -20489,8 +20710,8 @@
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="23" t="s">
-        <v>149</v>
+      <c r="C23" s="24" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
@@ -20498,21 +20719,21 @@
         <v>75</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>151</v>
+        <v>154</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>154</v>
+        <v>157</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
@@ -20520,197 +20741,197 @@
         <v>79</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>156</v>
+        <v>159</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>159</v>
+        <v>162</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>162</v>
+        <v>165</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>165</v>
+        <v>168</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>168</v>
+        <v>171</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>171</v>
+        <v>174</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>174</v>
+        <v>177</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>177</v>
+        <v>180</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>180</v>
+        <v>183</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>183</v>
+        <v>186</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>186</v>
+        <v>189</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>189</v>
+        <v>192</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>192</v>
+        <v>195</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>195</v>
+        <v>198</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>198</v>
+        <v>201</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>201</v>
+        <v>204</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>204</v>
+        <v>207</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C43" s="23" t="s">
-        <v>206</v>
+      <c r="C43" s="24" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">

--- a/Sprint_Report/TeamEReport.xlsx
+++ b/Sprint_Report/TeamEReport.xlsx
@@ -831,11 +831,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="296122275"/>
-        <c:axId val="1497330205"/>
+        <c:axId val="688225807"/>
+        <c:axId val="858514025"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="296122275"/>
+        <c:axId val="688225807"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -887,10 +887,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1497330205"/>
+        <c:crossAx val="858514025"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1497330205"/>
+        <c:axId val="858514025"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -954,7 +954,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="296122275"/>
+        <c:crossAx val="688225807"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -995,11 +995,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="202678943"/>
-        <c:axId val="446950256"/>
+        <c:axId val="859471244"/>
+        <c:axId val="926504897"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="202678943"/>
+        <c:axId val="859471244"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1051,10 +1051,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="446950256"/>
+        <c:crossAx val="926504897"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="446950256"/>
+        <c:axId val="926504897"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1118,7 +1118,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="202678943"/>
+        <c:crossAx val="859471244"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -18448,7 +18448,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="E5" s="8">
         <v>20.0</v>
@@ -18456,7 +18456,15 @@
       <c r="F5" s="8">
         <v>45.0</v>
       </c>
-      <c r="I5" s="24"/>
+      <c r="G5" s="8">
+        <v>30.0</v>
+      </c>
+      <c r="H5" s="8">
+        <v>40.0</v>
+      </c>
+      <c r="I5" s="24">
+        <v>46217.0</v>
+      </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="8" t="s">

--- a/Sprint_Report/TeamEReport.xlsx
+++ b/Sprint_Report/TeamEReport.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="211">
   <si>
     <t>Initials</t>
   </si>
@@ -182,9 +182,6 @@
     <t>No bigamy</t>
   </si>
   <si>
-    <t>Coding</t>
-  </si>
-  <si>
     <t>US13</t>
   </si>
   <si>
@@ -213,9 +210,6 @@
   </si>
   <si>
     <t>Aunts and uncles should not marry their nieces or nephews</t>
-  </si>
-  <si>
-    <t>coding</t>
   </si>
   <si>
     <t>US18</t>
@@ -254,7 +248,7 @@
     <t>Reject illegitimate dates</t>
   </si>
   <si>
-    <t>US 24</t>
+    <t>US24</t>
   </si>
   <si>
     <t>List Recent Births</t>
@@ -377,6 +371,18 @@
     <t>Multiple Births &lt;= 5</t>
   </si>
   <si>
+    <t>Keep Doing:</t>
+  </si>
+  <si>
+    <t>Completing Stories on Time: All 6 planned user stories were implemented and verified against the test GEDCOM file and individual unittest file by the sprint deadline.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good Communication: Team members met for weekly zoom meeting and communicated throughout the two weeks through messaging to resolve issues and keep team members updated. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relying on messages for updates: The team agreed to add a Kanban board as an additional form of documentation, so anyone can quickly check the most current status of what each member is working on without needing to ask in the group chat. It will track the current task a team member is working on (refactoring, testing, etc.) and will be updated as tasks change status, which will give the team a persistent resource rather than scattered messages. </t>
+  </si>
+  <si>
     <t>Not Started</t>
   </si>
   <si>
@@ -489,9 +495,6 @@
   </si>
   <si>
     <t>No more than one individual with the same name and birth date should appear in a GEDCOM file</t>
-  </si>
-  <si>
-    <t>US24</t>
   </si>
   <si>
     <t>Unique families by spouses</t>
@@ -666,7 +669,7 @@
     <numFmt numFmtId="166" formatCode="mm/dd"/>
     <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -706,6 +709,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Cambria"/>
@@ -737,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -787,7 +796,13 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -831,11 +846,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="688225807"/>
-        <c:axId val="858514025"/>
+        <c:axId val="767147329"/>
+        <c:axId val="135493324"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="688225807"/>
+        <c:axId val="767147329"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -887,10 +902,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="858514025"/>
+        <c:crossAx val="135493324"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="858514025"/>
+        <c:axId val="135493324"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -954,7 +969,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="688225807"/>
+        <c:crossAx val="767147329"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -995,11 +1010,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="859471244"/>
-        <c:axId val="926504897"/>
+        <c:axId val="164040390"/>
+        <c:axId val="1003280183"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="859471244"/>
+        <c:axId val="164040390"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1051,10 +1066,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="926504897"/>
+        <c:crossAx val="1003280183"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="926504897"/>
+        <c:axId val="1003280183"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1118,7 +1133,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="859471244"/>
+        <c:crossAx val="164040390"/>
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
@@ -3338,7 +3353,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
@@ -3346,10 +3361,10 @@
         <v>2.0</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>15</v>
@@ -3363,10 +3378,10 @@
         <v>3.0</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>5</v>
@@ -3380,10 +3395,10 @@
         <v>2.0</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>15</v>
@@ -3397,16 +3412,16 @@
         <v>3.0</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
@@ -3414,16 +3429,16 @@
         <v>3.0</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
@@ -3431,16 +3446,16 @@
         <v>3.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
@@ -3448,10 +3463,10 @@
         <v>4.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>5</v>
@@ -3462,10 +3477,13 @@
         <v>4.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
@@ -3473,10 +3491,10 @@
         <v>4.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>10</v>
@@ -3487,10 +3505,10 @@
         <v>2.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>10</v>
@@ -3504,10 +3522,10 @@
         <v>4.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>5</v>
@@ -3517,11 +3535,11 @@
       <c r="A25" s="8">
         <v>4.0</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>76</v>
+      <c r="B25" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>10</v>
@@ -3532,10 +3550,13 @@
         <v>4.0</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1"/>
@@ -4537,19 +4558,19 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F1" s="11"/>
     </row>
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F2" s="11"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F3" s="11"/>
     </row>
@@ -4559,13 +4580,13 @@
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F5" s="11"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F6" s="11"/>
     </row>
@@ -4575,7 +4596,7 @@
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F8" s="11"/>
     </row>
@@ -4604,22 +4625,22 @@
         <v>22</v>
       </c>
       <c r="B14" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="G14" s="13" t="s">
         <v>89</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>91</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -4643,7 +4664,7 @@
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B15" s="14">
         <v>42527.0</v>
@@ -4659,7 +4680,7 @@
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B16" s="14">
         <v>42540.0</v>
@@ -4684,7 +4705,7 @@
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B17" s="14">
         <v>42554.0</v>
@@ -4709,7 +4730,7 @@
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B18" s="14">
         <v>42568.0</v>
@@ -4734,7 +4755,7 @@
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B19" s="14">
         <v>42582.0</v>
@@ -8707,22 +8728,22 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="13" t="s">
         <v>89</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>91</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -8817,9 +8838,15 @@
       <c r="C5" s="8">
         <v>6.0</v>
       </c>
-      <c r="F5" s="11" t="str">
+      <c r="D5" s="8">
+        <v>288.0</v>
+      </c>
+      <c r="E5" s="8">
+        <v>278.0</v>
+      </c>
+      <c r="F5" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-23.09352518</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
@@ -8832,9 +8859,15 @@
       <c r="C6" s="8">
         <v>6.0</v>
       </c>
-      <c r="F6" s="11" t="str">
+      <c r="D6" s="8">
+        <v>130.0</v>
+      </c>
+      <c r="E6" s="8">
+        <v>230.0</v>
+      </c>
+      <c r="F6" s="11">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>-41.2173913</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
@@ -12852,19 +12885,19 @@
         <v>26</v>
       </c>
       <c r="E1" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>99</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
@@ -12930,7 +12963,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -13046,7 +13079,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>10</v>
@@ -13099,7 +13132,7 @@
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="B14" s="18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I14" s="10"/>
     </row>
@@ -13109,13 +13142,13 @@
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="B16" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I16" s="10"/>
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="B17" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I17" s="10"/>
     </row>
@@ -13129,13 +13162,13 @@
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="B20" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I20" s="10"/>
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I21" s="10"/>
     </row>
@@ -17089,19 +17122,19 @@
         <v>26</v>
       </c>
       <c r="E1" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>99</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="I1" s="19" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
@@ -17109,7 +17142,7 @@
         <v>40</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>5</v>
@@ -17167,7 +17200,7 @@
         <v>46</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>10</v>
@@ -17193,10 +17226,10 @@
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>10</v>
@@ -17222,10 +17255,10 @@
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>15</v>
@@ -17251,10 +17284,10 @@
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>15</v>
@@ -17286,7 +17319,7 @@
     <row r="13" ht="12.75" customHeight="1"/>
     <row r="14" ht="12.75" customHeight="1">
       <c r="B14" s="18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
@@ -17294,17 +17327,17 @@
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="B16" s="18" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" ht="62.25" customHeight="1">
       <c r="B17" s="21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" ht="63.75" customHeight="1">
       <c r="B18" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
@@ -17312,12 +17345,12 @@
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="B20" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" ht="61.5" customHeight="1">
       <c r="B21" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
@@ -18317,7 +18350,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="10.78"/>
-    <col customWidth="1" min="2" max="2" width="19.67"/>
+    <col customWidth="1" min="2" max="2" width="45.44"/>
     <col customWidth="1" min="3" max="26" width="10.78"/>
   </cols>
   <sheetData>
@@ -18335,19 +18368,19 @@
         <v>26</v>
       </c>
       <c r="E1" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>99</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="I1" s="19" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
@@ -18381,10 +18414,10 @@
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>5</v>
@@ -18439,10 +18472,10 @@
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>10</v>
@@ -18468,16 +18501,16 @@
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="E6" s="8">
         <v>80.0</v>
@@ -18485,40 +18518,82 @@
       <c r="F6" s="8">
         <v>60.0</v>
       </c>
+      <c r="G6" s="8">
+        <v>47.0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>45.0</v>
+      </c>
+      <c r="I6" s="24">
+        <v>46222.0</v>
+      </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="E7" s="8">
         <v>50.0</v>
       </c>
       <c r="F7" s="8">
         <v>50.0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>65.0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>45.0</v>
+      </c>
+      <c r="I7" s="24">
+        <v>46222.0</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1"/>
     <row r="9" ht="12.75" customHeight="1"/>
     <row r="10" ht="12.75" customHeight="1"/>
     <row r="11" ht="12.75" customHeight="1"/>
-    <row r="12" ht="12.75" customHeight="1"/>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="B12" s="25" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="13" ht="12.75" customHeight="1"/>
-    <row r="14" ht="12.75" customHeight="1"/>
-    <row r="15" ht="12.75" customHeight="1"/>
-    <row r="16" ht="12.75" customHeight="1"/>
+    <row r="14" ht="12.75" customHeight="1">
+      <c r="B14" s="25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" ht="38.25" customHeight="1">
+      <c r="B15" s="26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" ht="48.0" customHeight="1">
+      <c r="B16" s="26" t="s">
+        <v>117</v>
+      </c>
+    </row>
     <row r="17" ht="12.75" customHeight="1"/>
-    <row r="18" ht="12.75" customHeight="1"/>
-    <row r="19" ht="12.75" customHeight="1"/>
-    <row r="20" ht="12.75" customHeight="1"/>
+    <row r="18" ht="12.75" customHeight="1">
+      <c r="B18" s="25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" ht="37.5" customHeight="1">
+      <c r="B19" s="26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" ht="9.75" customHeight="1"/>
     <row r="21" ht="12.75" customHeight="1"/>
     <row r="22" ht="12.75" customHeight="1"/>
     <row r="23" ht="12.75" customHeight="1"/>
@@ -19514,7 +19589,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="10.78"/>
+    <col customWidth="1" min="1" max="1" width="10.78"/>
+    <col customWidth="1" min="2" max="2" width="23.44"/>
+    <col customWidth="1" min="3" max="26" width="10.78"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -19531,27 +19608,141 @@
         <v>26</v>
       </c>
       <c r="E1" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="H1" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="I1" s="19" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" ht="12.75" customHeight="1"/>
-    <row r="3" ht="12.75" customHeight="1"/>
-    <row r="4" ht="12.75" customHeight="1"/>
-    <row r="5" ht="12.75" customHeight="1"/>
-    <row r="6" ht="12.75" customHeight="1"/>
-    <row r="7" ht="12.75" customHeight="1"/>
+    </row>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="8">
+        <v>15.0</v>
+      </c>
+      <c r="F2" s="8">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="8">
+        <v>15.0</v>
+      </c>
+      <c r="F3" s="8">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="4" ht="12.75" customHeight="1">
+      <c r="A4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="8">
+        <v>20.0</v>
+      </c>
+      <c r="F4" s="8">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="5" ht="12.75" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="8">
+        <v>20.0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="A6" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="8">
+        <v>20.0</v>
+      </c>
+      <c r="F6" s="8">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="7" ht="12.75" customHeight="1">
+      <c r="A7" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="8">
+        <v>40.0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>60.0</v>
+      </c>
+    </row>
     <row r="8" ht="12.75" customHeight="1"/>
     <row r="9" ht="12.75" customHeight="1"/>
     <row r="10" ht="12.75" customHeight="1"/>
@@ -20574,7 +20765,7 @@
         <v>24</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -20607,8 +20798,8 @@
       <c r="B2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="25" t="s">
-        <v>119</v>
+      <c r="C2" s="27" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
@@ -20616,10 +20807,10 @@
         <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
@@ -20629,19 +20820,19 @@
       <c r="B4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>122</v>
+      <c r="C4" s="27" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
@@ -20649,10 +20840,10 @@
         <v>36</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
@@ -20660,10 +20851,10 @@
         <v>38</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
@@ -20671,10 +20862,10 @@
         <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
@@ -20682,10 +20873,10 @@
         <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
@@ -20693,10 +20884,10 @@
         <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>135</v>
+        <v>136</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
@@ -20706,8 +20897,8 @@
       <c r="B11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="25" t="s">
-        <v>136</v>
+      <c r="C11" s="27" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
@@ -20717,8 +20908,8 @@
       <c r="B12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="25" t="s">
-        <v>137</v>
+      <c r="C12" s="27" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
@@ -20726,338 +20917,338 @@
         <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>142</v>
+      <c r="C15" s="27" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>147</v>
+        <v>57</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>148</v>
+        <v>59</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="25"/>
+        <v>63</v>
+      </c>
+      <c r="C20" s="27"/>
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>62</v>
+        <v>151</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="25" t="s">
-        <v>152</v>
+      <c r="C23" s="27" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>155</v>
+        <v>74</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C25" s="25" t="s">
         <v>157</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C26" s="25" t="s">
         <v>159</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C27" s="25" t="s">
         <v>162</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C28" s="25" t="s">
         <v>165</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C29" s="25" t="s">
         <v>168</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C30" s="25" t="s">
         <v>171</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C31" s="25" t="s">
         <v>174</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C32" s="25" t="s">
         <v>177</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C33" s="25" t="s">
         <v>180</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C34" s="25" t="s">
         <v>183</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C35" s="25" t="s">
         <v>186</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C36" s="25" t="s">
         <v>189</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C37" s="25" t="s">
         <v>192</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C38" s="25" t="s">
         <v>195</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C39" s="25" t="s">
         <v>198</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C40" s="25" t="s">
         <v>201</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C41" s="25" t="s">
         <v>204</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C42" s="25" t="s">
         <v>207</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C43" s="25" t="s">
-        <v>209</v>
+        <v>73</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1">
